--- a/docs/shop-onboarding-wizard-2026-10/SHOP_REGISTRATION_SINGLE_FLOW_TRACKER_2026-10-30.xlsx
+++ b/docs/shop-onboarding-wizard-2026-10/SHOP_REGISTRATION_SINGLE_FLOW_TRACKER_2026-10-30.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="171">
   <si>
     <t>Shop registration — single flow, document window, pin after payment (owner brief 30 Oct 2026)</t>
   </si>
   <si>
-    <t>As of 30 Oct 2026, 23:30 IST. Branch fix/registration-single-flow, PR #298 into staging (CI running). Not on test.gokesari.com or gokesari.com yet. Design: docs/shop-onboarding-wizard-2026-10/FLOW_2026-10-30-b.md.</t>
+    <t>As of 31 Oct 2026, 00:30 IST. PR #298 merged into staging (685e1f2f) and live on test.gokesari.com since 30 Oct 18:37 UTC; follow-up fixes in a second PR. Not on gokesari.com. Design: docs/shop-onboarding-wizard-2026-10/FLOW_2026-10-30-b.md.</t>
   </si>
   <si>
     <t>#</t>
@@ -45,7 +45,7 @@
     <t>Done</t>
   </si>
   <si>
-    <t>Local; PR #298</t>
+    <t>test.gokesari.com (#298)</t>
   </si>
   <si>
     <t>One card on /sell and Seller Central → /shop/register. /shop/join forwards with ?code=/?ref=. /shop/join/{token} status pages unchanged.</t>
@@ -111,7 +111,7 @@
     <t>Page 4: payment</t>
   </si>
   <si>
-    <t>Unchanged checkout; sandbox payment tested locally.</t>
+    <t>Checkout unchanged. Local: sandbox payment passed. Staging: goes to HDFC Bank UAT gateway — not completed.</t>
   </si>
   <si>
     <t>-</t>
@@ -120,7 +120,10 @@
     <t>Page 5: address and location after payment</t>
   </si>
   <si>
-    <t>Owner chose 'pin after pay': address given before payment (shop needs one), corrected with the map pin after payment.</t>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Owner chose 'pin after pay': address given before payment (shop needs one), corrected with the map pin after payment. Verified locally; not reached on staging because staging's fee payment now goes to HDFC UAT.</t>
   </si>
   <si>
     <t>shop-registration-wizard.ts (step order); onboarding-wizard.tsx (ShopLocationStep)</t>
@@ -129,45 +132,42 @@
     <t>Google Maps fix</t>
   </si>
   <si>
+    <t>test.gokesari.com and gokesari.com</t>
+  </si>
+  <si>
+    <t>Cause: staging was built with a different browser key that Google refused (RefererNotAllowedMapError). Owner set the production key on staging in hPanel; the #298 build carries it and the map loads (verified 30 Oct). Code fallback for a refused key added.</t>
+  </si>
+  <si>
+    <t>lib/geo/provider.ts; map-picker.tsx; nearby-map.tsx</t>
+  </si>
+  <si>
+    <t>Android and iOS apps</t>
+  </si>
+  <si>
+    <t>WebView — no build needed</t>
+  </si>
+  <si>
+    <t>Both apps show the website; changes arrive with the web deploy. No platform differences in this flow.</t>
+  </si>
+  <si>
+    <t>mobile/README.md</t>
+  </si>
+  <si>
+    <t>Testing on Test (test.gokesari.com)</t>
+  </si>
+  <si>
+    <t>After merge of PR #298</t>
+  </si>
+  <si>
+    <t>Steps 1–6 pass on staging. Payment and address/location step blocked: staging uses PAYMENT_GATEWAY=HDFC (UAT), not SANDBOX.</t>
+  </si>
+  <si>
+    <t>Testing on Prod (gokesari.com)</t>
+  </si>
+  <si>
     <t>Blocked</t>
   </si>
   <si>
-    <t>Code fallback in PR #298</t>
-  </si>
-  <si>
-    <t>Cause: staging browser key refused (RefererNotAllowedMapError); production OK. Needs the owner to add https://test.gokesari.com/* to the key's website restrictions in Google Cloud Console. Code fallback added for a refused key.</t>
-  </si>
-  <si>
-    <t>lib/geo/provider.ts; map-picker.tsx; nearby-map.tsx</t>
-  </si>
-  <si>
-    <t>Android and iOS apps</t>
-  </si>
-  <si>
-    <t>WebView — no build needed</t>
-  </si>
-  <si>
-    <t>Both apps show the website; changes arrive with the web deploy. No platform differences in this flow.</t>
-  </si>
-  <si>
-    <t>mobile/README.md</t>
-  </si>
-  <si>
-    <t>Testing on Test (test.gokesari.com)</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>After merge of PR #298</t>
-  </si>
-  <si>
-    <t>Needs: merge into staging, the wizard flag on for staging (Admin → Feature flags), and the Maps key fix.</t>
-  </si>
-  <si>
-    <t>Testing on Prod (gokesari.com)</t>
-  </si>
-  <si>
     <t>Owner-approved release window</t>
   </si>
   <si>
@@ -345,10 +345,34 @@
     <t>Script + Places load, no auth error</t>
   </si>
   <si>
+    <t>REG-1</t>
+  </si>
+  <si>
+    <t>Regression: whole suite</t>
+  </si>
+  <si>
+    <t>see UT-4</t>
+  </si>
+  <si>
+    <t>PRD-1</t>
+  </si>
+  <si>
+    <t>Smoke on gokesari.com</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>Not run</t>
+  </si>
+  <si>
+    <t>after an owner-approved release</t>
+  </si>
+  <si>
     <t>MAP-2</t>
   </si>
   <si>
-    <t>Maps on test.gokesari.com</t>
+    <t>Maps on test.gokesari.com before the fix</t>
   </si>
   <si>
     <t>Staging</t>
@@ -357,40 +381,91 @@
     <t>Fail</t>
   </si>
   <si>
-    <t>RefererNotAllowedMapError — owner action in Google Cloud Console</t>
-  </si>
-  <si>
-    <t>REG-1</t>
-  </si>
-  <si>
-    <t>Regression: whole suite</t>
-  </si>
-  <si>
-    <t>see UT-4</t>
-  </si>
-  <si>
-    <t>STG-1</t>
-  </si>
-  <si>
-    <t>Registration flow on test.gokesari.com</t>
-  </si>
-  <si>
-    <t>Not run</t>
-  </si>
-  <si>
-    <t>after merge + wizard flag</t>
-  </si>
-  <si>
-    <t>PRD-1</t>
-  </si>
-  <si>
-    <t>Smoke on gokesari.com</t>
-  </si>
-  <si>
-    <t>Production</t>
-  </si>
-  <si>
-    <t>after an owner-approved release</t>
+    <t>RefererNotAllowedMapError with the old staging key</t>
+  </si>
+  <si>
+    <t>MAP-3</t>
+  </si>
+  <si>
+    <t>Maps on test.gokesari.com after the owner's key change</t>
+  </si>
+  <si>
+    <t>Production key (…UffY) built in; map and Places load</t>
+  </si>
+  <si>
+    <t>ST-1</t>
+  </si>
+  <si>
+    <t>/sell one card → /shop/register</t>
+  </si>
+  <si>
+    <t>ST-2</t>
+  </si>
+  <si>
+    <t>/shop/join?code → /shop/register?ref</t>
+  </si>
+  <si>
+    <t>ST-3</t>
+  </si>
+  <si>
+    <t>Seller Central with no shop: one card</t>
+  </si>
+  <si>
+    <t>ST-4</t>
+  </si>
+  <si>
+    <t>Code required on staging; test code T47BC8PU</t>
+  </si>
+  <si>
+    <t>ST-5</t>
+  </si>
+  <si>
+    <t>Referral → email → Yes / No</t>
+  </si>
+  <si>
+    <t>ST-6</t>
+  </si>
+  <si>
+    <t>Document window, 5 lines with Validate</t>
+  </si>
+  <si>
+    <t>Staging provider: all 'Our team will check' for test numbers</t>
+  </si>
+  <si>
+    <t>ST-7</t>
+  </si>
+  <si>
+    <t>Confirm details → review (no map before payment) → shop created</t>
+  </si>
+  <si>
+    <t>QA Staging Stores 298</t>
+  </si>
+  <si>
+    <t>ST-8</t>
+  </si>
+  <si>
+    <t>Payment</t>
+  </si>
+  <si>
+    <t>Goes to HDFC UAT gateway; card details not entered by Claude</t>
+  </si>
+  <si>
+    <t>ST-9</t>
+  </si>
+  <si>
+    <t>Address and location after payment</t>
+  </si>
+  <si>
+    <t>Needs ST-8</t>
+  </si>
+  <si>
+    <t>GOV-STG</t>
+  </si>
+  <si>
+    <t>GSTIN / Shop Act / FSSAI / Udyam on the staging provider</t>
+  </si>
+  <si>
+    <t>Clear 'Our team will check' states; a real GSTIN is needed to see Verified</t>
   </si>
   <si>
     <t>Open items and decisions</t>
@@ -405,7 +480,7 @@
     <t>Who</t>
   </si>
   <si>
-    <t>Add https://test.gokesari.com/* to the staging Maps browser key's website restrictions</t>
+    <t>Production release window</t>
   </si>
   <si>
     <t>Owner</t>
@@ -414,30 +489,6 @@
     <t>Open</t>
   </si>
   <si>
-    <t>Google Cloud Console → Credentials</t>
-  </si>
-  <si>
-    <t>Merge PR #298 into staging after CI</t>
-  </si>
-  <si>
-    <t>Claude / owner</t>
-  </si>
-  <si>
-    <t>Then run STG-1</t>
-  </si>
-  <si>
-    <t>Switch shop_onboarding_wizard_enabled on for test.gokesari.com</t>
-  </si>
-  <si>
-    <t>Admin</t>
-  </si>
-  <si>
-    <t>Without it, /shop/register shows the long form to non-admins</t>
-  </si>
-  <si>
-    <t>Production release window</t>
-  </si>
-  <si>
     <t>One release at a time (DEPLOYMENT.md §3)</t>
   </si>
   <si>
@@ -454,6 +505,27 @@
   </si>
   <si>
     <t>Carried from 30 Oct flow</t>
+  </si>
+  <si>
+    <t>Staging fee payment goes to HDFC UAT — switch back to SANDBOX or pay with HDFC's test card</t>
+  </si>
+  <si>
+    <t>Blocks ST-8 / ST-9</t>
+  </si>
+  <si>
+    <t>Dealer-role account sees the wizard but step 1 says 'no permission'</t>
+  </si>
+  <si>
+    <t>Existing; could tell dealers to switch to their customer account</t>
+  </si>
+  <si>
+    <t>Staging test data: shop 'QA Staging Stores 298' (unpaid) and referral code T47BC8PU</t>
+  </si>
+  <si>
+    <t>Owner / QA</t>
+  </si>
+  <si>
+    <t>Delete or keep for the next run</t>
   </si>
 </sst>
 </file>
@@ -499,12 +571,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
+        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
+        <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1093,17 +1165,17 @@
       <c r="B13" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>9</v>
+      <c r="C13" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1111,10 +1183,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="7" t="s">
         <v>38</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>39</v>
@@ -1153,14 +1225,14 @@
       <c r="B16" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>33</v>
@@ -1171,10 +1243,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>50</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>38</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>51</v>
@@ -1194,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1511,27 +1583,27 @@
         <v>111</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="D22" s="9" t="s">
         <v>116</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>117</v>
@@ -1545,30 +1617,200 @@
         <v>119</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D23" s="9" t="s">
         <v>120</v>
       </c>
+      <c r="D23" s="8" t="s">
+        <v>121</v>
+      </c>
       <c r="E23" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D24" s="9" t="s">
         <v>120</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -1591,12 +1833,12 @@
   <sheetData>
     <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1604,10 +1846,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>4</v>
@@ -1618,104 +1860,104 @@
     </row>
     <row r="5" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/docs/shop-onboarding-wizard-2026-10/SHOP_REGISTRATION_SINGLE_FLOW_TRACKER_2026-10-30.xlsx
+++ b/docs/shop-onboarding-wizard-2026-10/SHOP_REGISTRATION_SINGLE_FLOW_TRACKER_2026-10-30.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="178">
   <si>
     <t>Shop registration — single flow, document window, pin after payment (owner brief 30 Oct 2026)</t>
   </si>
   <si>
-    <t>As of 31 Oct 2026, 00:30 IST. PR #298 merged into staging (685e1f2f) and live on test.gokesari.com since 30 Oct 18:37 UTC; follow-up fixes in a second PR. Not on gokesari.com. Design: docs/shop-onboarding-wizard-2026-10/FLOW_2026-10-30-b.md.</t>
+    <t>As of 31 Oct 2026, 10:00 IST. PR #298 and #299 merged into staging and live on test.gokesari.com; the whole flow passed there on 31 Oct. Not on gokesari.com (waits for an owner-approved release). Design: docs/shop-onboarding-wizard-2026-10/FLOW_2026-10-30-b.md.</t>
   </si>
   <si>
     <t>#</t>
@@ -45,7 +45,7 @@
     <t>Done</t>
   </si>
   <si>
-    <t>test.gokesari.com (#298)</t>
+    <t>test.gokesari.com (#298, #299)</t>
   </si>
   <si>
     <t>One card on /sell and Seller Central → /shop/register. /shop/join forwards with ?code=/?ref=. /shop/join/{token} status pages unchanged.</t>
@@ -111,7 +111,7 @@
     <t>Page 4: payment</t>
   </si>
   <si>
-    <t>Checkout unchanged. Local: sandbox payment passed. Staging: goes to HDFC Bank UAT gateway — not completed.</t>
+    <t>Checkout unchanged. Staging (SANDBOX): paid on the built-in sandbox page. Found and fixed a receipt-number bug that stopped payments being recorded (#299).</t>
   </si>
   <si>
     <t>-</t>
@@ -120,10 +120,7 @@
     <t>Page 5: address and location after payment</t>
   </si>
   <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>Owner chose 'pin after pay': address given before payment (shop needs one), corrected with the map pin after payment. Verified locally; not reached on staging because staging's fee payment now goes to HDFC UAT.</t>
+    <t>Owner chose 'pin after pay'. Staging: after payment and approval, step 8 showed the address pre-filled and the Google map; Confirm location saved address, landmark and pin.</t>
   </si>
   <si>
     <t>shop-registration-wizard.ts (step order); onboarding-wizard.tsx (ShopLocationStep)</t>
@@ -159,7 +156,7 @@
     <t>After merge of PR #298</t>
   </si>
   <si>
-    <t>Steps 1–6 pass on staging. Payment and address/location step blocked: staging uses PAYMENT_GATEWAY=HDFC (UAT), not SANDBOX.</t>
+    <t>Whole flow passed on staging (31 Oct): one card, screen 2, Yes/No, window with Validate, confirm, sandbox payment, address and map location.</t>
   </si>
   <si>
     <t>Testing on Prod (gokesari.com)</t>
@@ -174,6 +171,18 @@
     <t>Owner chose 'staging now, Prod later'. Read-only smoke checks after release; no payment on production.</t>
   </si>
   <si>
+    <t>Payment receipt number fix (found during testing)</t>
+  </si>
+  <si>
+    <t>test.gokesari.com (#299)</t>
+  </si>
+  <si>
+    <t>Receipt = highest number this year + 1 (was row count + 1, which collided after rows were deleted). Must go to production with the next release.</t>
+  </si>
+  <si>
+    <t>src/server/services/shop-payments.ts; tests/integration/shop-payment-reference.test.ts</t>
+  </si>
+  <si>
     <t>Test results</t>
   </si>
   <si>
@@ -447,7 +456,7 @@
     <t>Payment</t>
   </si>
   <si>
-    <t>Goes to HDFC UAT gateway; card details not entered by Claude</t>
+    <t>Sandbox page; captured; recorded after #299 (fee PAID)</t>
   </si>
   <si>
     <t>ST-9</t>
@@ -456,7 +465,7 @@
     <t>Address and location after payment</t>
   </si>
   <si>
-    <t>Needs ST-8</t>
+    <t>Address pre-filled, Google map, Confirm location saved address + landmark + pin (18.5167, 73.8415)</t>
   </si>
   <si>
     <t>GOV-STG</t>
@@ -468,6 +477,18 @@
     <t>Clear 'Our team will check' states; a real GSTIN is needed to see Verified</t>
   </si>
   <si>
+    <t>UT-5</t>
+  </si>
+  <si>
+    <t>Receipt numbers: gap after deleted rows; new year starts at 1</t>
+  </si>
+  <si>
+    <t>Local, both layouts</t>
+  </si>
+  <si>
+    <t>shop-payment-reference.test.ts + payment tests 55 / 55 each</t>
+  </si>
+  <si>
     <t>Open items and decisions</t>
   </si>
   <si>
@@ -507,12 +528,6 @@
     <t>Carried from 30 Oct flow</t>
   </si>
   <si>
-    <t>Staging fee payment goes to HDFC UAT — switch back to SANDBOX or pay with HDFC's test card</t>
-  </si>
-  <si>
-    <t>Blocks ST-8 / ST-9</t>
-  </si>
-  <si>
     <t>Dealer-role account sees the wizard but step 1 says 'no permission'</t>
   </si>
   <si>
@@ -525,7 +540,13 @@
     <t>Owner / QA</t>
   </si>
   <si>
-    <t>Delete or keep for the next run</t>
+    <t>Shops 'QA Staging Stores 298' (unpaid) and 'QA Staging Full Run 298' (live, QA waiver); code T47BC8PU (2 of 5 uses). Delete or keep.</t>
+  </si>
+  <si>
+    <t>Release #298 + #299 to gokesari.com (receipt fix protects production payments)</t>
+  </si>
+  <si>
+    <t>One release at a time; post-deploy check after (DEPLOYMENT.md §3)</t>
   </si>
 </sst>
 </file>
@@ -552,7 +573,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -567,11 +588,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDCFCE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -597,7 +613,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -613,9 +629,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -957,7 +970,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1165,17 +1178,17 @@
       <c r="B13" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>35</v>
+      <c r="C13" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1183,19 +1196,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1203,19 +1216,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="F15" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1223,16 +1236,16 @@
         <v>12</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>48</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>33</v>
@@ -1243,19 +1256,39 @@
         <v>13</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="D17" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1266,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1278,145 +1311,145 @@
   <sheetData>
     <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>33</v>
@@ -1424,16 +1457,16 @@
     </row>
     <row r="12" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>33</v>
@@ -1441,84 +1474,84 @@
     </row>
     <row r="13" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>33</v>
@@ -1526,135 +1559,135 @@
     </row>
     <row r="18" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>119</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>124</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>120</v>
-      </c>
       <c r="D24" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>33</v>
@@ -1662,16 +1695,16 @@
     </row>
     <row r="26" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>33</v>
@@ -1679,16 +1712,16 @@
     </row>
     <row r="27" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>33</v>
@@ -1696,33 +1729,33 @@
     </row>
     <row r="28" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>33</v>
@@ -1730,87 +1763,104 @@
     </row>
     <row r="30" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>116</v>
+        <v>123</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>116</v>
+        <v>123</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -1833,12 +1883,12 @@
   <sheetData>
     <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1846,10 +1896,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>4</v>
@@ -1863,16 +1913,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1880,16 +1930,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1897,67 +1947,67 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>157</v>
-      </c>
       <c r="E8" s="5" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
